--- a/target/test-classes/FlightSaudiadata.xlsx
+++ b/target/test-classes/FlightSaudiadata.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Ravibhushan.Kumar\eclipse-workspace\Project_SAUDIA\src\test\resources\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A6159542-987F-4305-91EA-86018BFA64C0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{72D3A23E-F11C-4D71-8B08-3F6E03154401}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="19440" windowHeight="14040" xr2:uid="{7DC593AB-2AC3-4143-ABC1-B9CC8773C1AC}"/>
   </bookViews>
@@ -40,7 +40,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="170" uniqueCount="76">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1172" uniqueCount="121">
   <si>
     <t>TestCaseID</t>
   </si>
@@ -186,88 +186,223 @@
     <t>Multi-city</t>
   </si>
   <si>
-    <t>25-Sep-2026</t>
+    <t>TC-06:-Verify user is able to create booking</t>
+  </si>
+  <si>
+    <t>Krishna</t>
+  </si>
+  <si>
+    <t>24-Sep-2005</t>
+  </si>
+  <si>
+    <t>PASS3421</t>
+  </si>
+  <si>
+    <t>Sudah</t>
+  </si>
+  <si>
+    <t>Kant</t>
+  </si>
+  <si>
+    <t>15-Sep-2001</t>
+  </si>
+  <si>
+    <t>PASS34025</t>
+  </si>
+  <si>
+    <t>TC-04:-Verify user is able to create booking</t>
+  </si>
+  <si>
+    <t xml:space="preserve">TC-02:-Verify user is able to create booking </t>
+  </si>
+  <si>
+    <t>1</t>
+  </si>
+  <si>
+    <t>Baleshwar</t>
+  </si>
+  <si>
+    <t xml:space="preserve">TC-08:-Verify user is able to create booking </t>
+  </si>
+  <si>
+    <t>Rajvir</t>
+  </si>
+  <si>
+    <t>24-Sep-2006</t>
+  </si>
+  <si>
+    <t>PASS342523</t>
+  </si>
+  <si>
+    <t>PASS34217</t>
+  </si>
+  <si>
+    <t>Balashewar</t>
+  </si>
+  <si>
+    <t>saket</t>
+  </si>
+  <si>
+    <t>12-Oct-2026</t>
+  </si>
+  <si>
+    <t>14-Oct-2026</t>
+  </si>
+  <si>
+    <t>16-Oct-2026</t>
+  </si>
+  <si>
+    <t>17-Oct-2026</t>
+  </si>
+  <si>
+    <t>19-Oct-2026</t>
+  </si>
+  <si>
+    <t>21-Oct-2026</t>
+  </si>
+  <si>
+    <t>18-Oct-2026</t>
+  </si>
+  <si>
+    <t xml:space="preserve">TC-03:-Verify user is able to create booking </t>
+  </si>
+  <si>
+    <t>TC-07:-Verify user is able to create booking</t>
+  </si>
+  <si>
+    <t xml:space="preserve">TC-09:-Verify user is able to create booking </t>
+  </si>
+  <si>
+    <t xml:space="preserve"> Family trip </t>
+  </si>
+  <si>
+    <t>paymentMethod</t>
+  </si>
+  <si>
+    <t>CardNumber</t>
+  </si>
+  <si>
+    <t>CardHolderName</t>
+  </si>
+  <si>
+    <t>SecurityCode</t>
+  </si>
+  <si>
+    <t>Saved cards</t>
+  </si>
+  <si>
+    <t>4111-1111-1111-1111</t>
+  </si>
+  <si>
+    <t>Ravi bhushan</t>
+  </si>
+  <si>
+    <t>Expirymonth</t>
+  </si>
+  <si>
+    <t>ExpiryYear</t>
+  </si>
+  <si>
+    <t>06</t>
+  </si>
+  <si>
+    <t>2034</t>
+  </si>
+  <si>
+    <t>123</t>
+  </si>
+  <si>
+    <t>Use a different card</t>
+  </si>
+  <si>
+    <t>TC-01:-Verify user is able to create booking</t>
+  </si>
+  <si>
+    <t>TC-02:-Verify user is able to create booking</t>
   </si>
   <si>
     <t>TC-03:-Verify user is able to create booking</t>
   </si>
   <si>
-    <t>TC-06:-Verify user is able to create booking</t>
-  </si>
-  <si>
-    <t>Bal</t>
-  </si>
-  <si>
-    <t>Krishna</t>
-  </si>
-  <si>
-    <t>24-Sep-2005</t>
-  </si>
-  <si>
-    <t>PASS3421</t>
-  </si>
-  <si>
-    <t>Sudah</t>
-  </si>
-  <si>
-    <t>Kant</t>
-  </si>
-  <si>
-    <t>15-Sep-2001</t>
-  </si>
-  <si>
-    <t>PASS34025</t>
-  </si>
-  <si>
-    <t>TC-04:-Verify user is able to create booking</t>
+    <t xml:space="preserve">TC-04:-Verify user is able to create booking </t>
+  </si>
+  <si>
+    <t xml:space="preserve">TC-05:-Verify user is able to create booking </t>
+  </si>
+  <si>
+    <t>TC-08:-Verify user is able to create booking</t>
+  </si>
+  <si>
+    <t xml:space="preserve">TC-10:-Verify user is able to create booking </t>
+  </si>
+  <si>
+    <t>SADAD</t>
+  </si>
+  <si>
+    <t>OTP</t>
+  </si>
+  <si>
+    <t>1234</t>
+  </si>
+  <si>
+    <t xml:space="preserve">TC-06:-Verify user is able to create booking </t>
+  </si>
+  <si>
+    <t>20-Oct-2026</t>
+  </si>
+  <si>
+    <t xml:space="preserve">TC-07:-Verify user is able to create booking </t>
   </si>
   <si>
     <t xml:space="preserve">TC-01:-Verify user is able to create booking </t>
   </si>
   <si>
-    <t xml:space="preserve">TC-02:-Verify user is able to create booking </t>
-  </si>
-  <si>
-    <t>1</t>
-  </si>
-  <si>
-    <t xml:space="preserve">TC-07:-Verify user is able to create booking </t>
-  </si>
-  <si>
-    <t>Baleshwar</t>
-  </si>
-  <si>
-    <t xml:space="preserve">TC-08:-Verify user is able to create booking </t>
-  </si>
-  <si>
-    <t>Rajvir</t>
-  </si>
-  <si>
-    <t>24-Sep-2006</t>
-  </si>
-  <si>
-    <t>PASS342523</t>
-  </si>
-  <si>
-    <t>PASS34217</t>
-  </si>
-  <si>
-    <t>27-Sep-2026</t>
-  </si>
-  <si>
-    <t>29-Sep-2026</t>
-  </si>
-  <si>
-    <t>26-Sep-2026</t>
-  </si>
-  <si>
-    <t>28-Sep-2026</t>
-  </si>
-  <si>
-    <t>Balashewar</t>
-  </si>
-  <si>
-    <t>saket</t>
+    <t>23-Oct-2026</t>
+  </si>
+  <si>
+    <t>22-Oct-2026</t>
+  </si>
+  <si>
+    <t xml:space="preserve">TC-11:-Verify user is able to create booking </t>
+  </si>
+  <si>
+    <t xml:space="preserve">TC-12:-Verify user is able to create booking </t>
+  </si>
+  <si>
+    <t>TC-14:-Verify user is able to create booking</t>
+  </si>
+  <si>
+    <t xml:space="preserve">TC-18:-Verify user is able to create booking </t>
+  </si>
+  <si>
+    <t xml:space="preserve">TC-19:-Verify user is able to create booking </t>
+  </si>
+  <si>
+    <t xml:space="preserve">TC-20:-Verify user is able to create booking </t>
+  </si>
+  <si>
+    <t>TC-22:-Verify user is able to create booking</t>
+  </si>
+  <si>
+    <t>TC-13:-Verify user is able to create booking</t>
+  </si>
+  <si>
+    <t xml:space="preserve">TC-15:-Verify user is able to create booking </t>
+  </si>
+  <si>
+    <t>TC-16:-Verify user is able to create booking</t>
+  </si>
+  <si>
+    <t xml:space="preserve">TC-17:-Verify user is able to create booking </t>
+  </si>
+  <si>
+    <t>TC-21:-Verify user is able to create booking</t>
+  </si>
+  <si>
+    <t xml:space="preserve">TC-23:-Verify user is able to create booking </t>
+  </si>
+  <si>
+    <t>TC-24:-Verify user is able to create booking</t>
   </si>
 </sst>
 </file>
@@ -647,7 +782,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{4775AB72-AEA3-4520-9C23-DEE07D8ADD12}">
-  <dimension ref="A1:AD2"/>
+  <dimension ref="A1:AK25"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="62.85546875" customWidth="1"/>
@@ -667,9 +802,14 @@
     <col min="28" max="28" width="16.42578125" customWidth="1"/>
     <col min="29" max="29" width="18.85546875" customWidth="1"/>
     <col min="30" max="30" width="22.85546875" customWidth="1"/>
+    <col min="31" max="31" width="16.42578125" customWidth="1"/>
+    <col min="32" max="32" width="21.42578125" customWidth="1"/>
+    <col min="33" max="33" width="15.28515625" customWidth="1"/>
+    <col min="34" max="34" width="16.42578125" customWidth="1"/>
+    <col min="35" max="35" width="15" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:30" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:37" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -760,10 +900,31 @@
       <c r="AD1" t="s">
         <v>32</v>
       </c>
-    </row>
-    <row r="2" spans="1:30" x14ac:dyDescent="0.25">
+      <c r="AE1" s="1" t="s">
+        <v>78</v>
+      </c>
+      <c r="AF1" s="1" t="s">
+        <v>79</v>
+      </c>
+      <c r="AG1" s="1" t="s">
+        <v>80</v>
+      </c>
+      <c r="AH1" s="1" t="s">
+        <v>81</v>
+      </c>
+      <c r="AI1" s="1" t="s">
+        <v>85</v>
+      </c>
+      <c r="AJ1" s="1" t="s">
+        <v>86</v>
+      </c>
+      <c r="AK1" s="1" t="s">
+        <v>99</v>
+      </c>
+    </row>
+    <row r="2" spans="1:37" x14ac:dyDescent="0.25">
       <c r="A2" s="1" t="s">
-        <v>60</v>
+        <v>104</v>
       </c>
       <c r="B2" s="1" t="s">
         <v>18</v>
@@ -775,14 +936,14 @@
         <v>17</v>
       </c>
       <c r="E2" s="1" t="s">
-        <v>48</v>
+        <v>72</v>
       </c>
       <c r="F2" s="1"/>
       <c r="G2" s="1" t="s">
-        <v>42</v>
+        <v>10</v>
       </c>
       <c r="H2" s="1" t="s">
-        <v>11</v>
+        <v>77</v>
       </c>
       <c r="I2" s="1" t="s">
         <v>12</v>
@@ -796,19 +957,19 @@
         <v>40</v>
       </c>
       <c r="P2" s="1" t="s">
+        <v>65</v>
+      </c>
+      <c r="Q2" s="1" t="s">
+        <v>49</v>
+      </c>
+      <c r="R2" s="1" t="s">
+        <v>50</v>
+      </c>
+      <c r="S2" s="1" t="s">
+        <v>23</v>
+      </c>
+      <c r="T2" s="1" t="s">
         <v>51</v>
-      </c>
-      <c r="Q2" s="1" t="s">
-        <v>52</v>
-      </c>
-      <c r="R2" s="1" t="s">
-        <v>53</v>
-      </c>
-      <c r="S2" s="1" t="s">
-        <v>23</v>
-      </c>
-      <c r="T2" s="1" t="s">
-        <v>54</v>
       </c>
       <c r="U2" s="1" t="s">
         <v>26</v>
@@ -820,25 +981,1685 @@
         <v>40</v>
       </c>
       <c r="X2" s="1" t="s">
+        <v>52</v>
+      </c>
+      <c r="Y2" s="1" t="s">
+        <v>53</v>
+      </c>
+      <c r="Z2" s="2" t="s">
+        <v>54</v>
+      </c>
+      <c r="AA2" s="1" t="s">
+        <v>23</v>
+      </c>
+      <c r="AB2" s="1" t="s">
         <v>55</v>
-      </c>
-      <c r="Y2" s="1" t="s">
-        <v>56</v>
-      </c>
-      <c r="Z2" s="2" t="s">
-        <v>57</v>
-      </c>
-      <c r="AA2" s="1" t="s">
-        <v>23</v>
-      </c>
-      <c r="AB2" s="1" t="s">
-        <v>58</v>
       </c>
       <c r="AC2" s="1" t="s">
         <v>41</v>
       </c>
       <c r="AD2" s="1" t="s">
         <v>27</v>
+      </c>
+      <c r="AE2" s="1" t="s">
+        <v>90</v>
+      </c>
+      <c r="AF2" s="1" t="s">
+        <v>83</v>
+      </c>
+      <c r="AG2" s="1" t="s">
+        <v>84</v>
+      </c>
+      <c r="AH2" s="1" t="s">
+        <v>89</v>
+      </c>
+      <c r="AI2" s="1" t="s">
+        <v>87</v>
+      </c>
+      <c r="AJ2" s="1" t="s">
+        <v>88</v>
+      </c>
+    </row>
+    <row r="3" spans="1:37" x14ac:dyDescent="0.25">
+      <c r="A3" s="1" t="s">
+        <v>57</v>
+      </c>
+      <c r="B3" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="C3" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="D3" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="E3" s="1" t="s">
+        <v>72</v>
+      </c>
+      <c r="F3" s="1"/>
+      <c r="G3" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="H3" s="1" t="s">
+        <v>77</v>
+      </c>
+      <c r="I3" s="1" t="s">
+        <v>12</v>
+      </c>
+      <c r="J3" s="1"/>
+      <c r="K3" s="1"/>
+      <c r="L3" s="1" t="s">
+        <v>20</v>
+      </c>
+      <c r="O3" s="1" t="s">
+        <v>40</v>
+      </c>
+      <c r="P3" s="1" t="s">
+        <v>65</v>
+      </c>
+      <c r="Q3" s="1" t="s">
+        <v>49</v>
+      </c>
+      <c r="R3" s="1" t="s">
+        <v>50</v>
+      </c>
+      <c r="S3" s="1" t="s">
+        <v>23</v>
+      </c>
+      <c r="T3" s="1" t="s">
+        <v>51</v>
+      </c>
+      <c r="U3" s="1" t="s">
+        <v>26</v>
+      </c>
+      <c r="V3" s="1" t="s">
+        <v>27</v>
+      </c>
+      <c r="W3" s="1" t="s">
+        <v>40</v>
+      </c>
+      <c r="X3" s="1" t="s">
+        <v>52</v>
+      </c>
+      <c r="Y3" s="1" t="s">
+        <v>53</v>
+      </c>
+      <c r="Z3" s="2" t="s">
+        <v>54</v>
+      </c>
+      <c r="AA3" s="1" t="s">
+        <v>23</v>
+      </c>
+      <c r="AB3" s="1" t="s">
+        <v>55</v>
+      </c>
+      <c r="AC3" s="1" t="s">
+        <v>41</v>
+      </c>
+      <c r="AD3" s="1" t="s">
+        <v>27</v>
+      </c>
+      <c r="AE3" s="1" t="s">
+        <v>82</v>
+      </c>
+      <c r="AK3" s="1" t="s">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="4" spans="1:37" x14ac:dyDescent="0.25">
+      <c r="A4" s="1" t="s">
+        <v>74</v>
+      </c>
+      <c r="B4" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="C4" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="D4" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="E4" s="1" t="s">
+        <v>102</v>
+      </c>
+      <c r="F4" s="1"/>
+      <c r="G4" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="H4" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="I4" s="1" t="s">
+        <v>12</v>
+      </c>
+      <c r="J4" s="1"/>
+      <c r="K4" s="1"/>
+      <c r="L4" s="1" t="s">
+        <v>20</v>
+      </c>
+      <c r="O4" s="1" t="s">
+        <v>40</v>
+      </c>
+      <c r="P4" s="1" t="s">
+        <v>65</v>
+      </c>
+      <c r="Q4" s="1" t="s">
+        <v>49</v>
+      </c>
+      <c r="R4" s="1" t="s">
+        <v>50</v>
+      </c>
+      <c r="S4" s="1" t="s">
+        <v>23</v>
+      </c>
+      <c r="T4" s="1" t="s">
+        <v>51</v>
+      </c>
+      <c r="U4" s="1" t="s">
+        <v>26</v>
+      </c>
+      <c r="V4" s="1" t="s">
+        <v>27</v>
+      </c>
+      <c r="W4" s="1" t="s">
+        <v>40</v>
+      </c>
+      <c r="X4" s="1" t="s">
+        <v>52</v>
+      </c>
+      <c r="Y4" s="1" t="s">
+        <v>53</v>
+      </c>
+      <c r="Z4" s="2" t="s">
+        <v>54</v>
+      </c>
+      <c r="AA4" s="1" t="s">
+        <v>23</v>
+      </c>
+      <c r="AB4" s="1" t="s">
+        <v>55</v>
+      </c>
+      <c r="AC4" s="1" t="s">
+        <v>41</v>
+      </c>
+      <c r="AD4" s="1" t="s">
+        <v>27</v>
+      </c>
+      <c r="AE4" s="1" t="s">
+        <v>90</v>
+      </c>
+      <c r="AF4" s="1" t="s">
+        <v>83</v>
+      </c>
+      <c r="AG4" s="1" t="s">
+        <v>84</v>
+      </c>
+      <c r="AH4" s="1" t="s">
+        <v>89</v>
+      </c>
+      <c r="AI4" s="1" t="s">
+        <v>87</v>
+      </c>
+      <c r="AJ4" s="1" t="s">
+        <v>88</v>
+      </c>
+    </row>
+    <row r="5" spans="1:37" x14ac:dyDescent="0.25">
+      <c r="A5" s="1" t="s">
+        <v>94</v>
+      </c>
+      <c r="B5" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="C5" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="D5" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="E5" s="1" t="s">
+        <v>102</v>
+      </c>
+      <c r="F5" s="1"/>
+      <c r="G5" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="H5" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="I5" s="1" t="s">
+        <v>12</v>
+      </c>
+      <c r="J5" s="1"/>
+      <c r="K5" s="1"/>
+      <c r="L5" s="1" t="s">
+        <v>20</v>
+      </c>
+      <c r="O5" s="1" t="s">
+        <v>40</v>
+      </c>
+      <c r="P5" s="1" t="s">
+        <v>65</v>
+      </c>
+      <c r="Q5" s="1" t="s">
+        <v>49</v>
+      </c>
+      <c r="R5" s="1" t="s">
+        <v>50</v>
+      </c>
+      <c r="S5" s="1" t="s">
+        <v>23</v>
+      </c>
+      <c r="T5" s="1" t="s">
+        <v>51</v>
+      </c>
+      <c r="U5" s="1" t="s">
+        <v>26</v>
+      </c>
+      <c r="V5" s="1" t="s">
+        <v>27</v>
+      </c>
+      <c r="W5" s="1" t="s">
+        <v>40</v>
+      </c>
+      <c r="X5" s="1" t="s">
+        <v>52</v>
+      </c>
+      <c r="Y5" s="1" t="s">
+        <v>53</v>
+      </c>
+      <c r="Z5" s="2" t="s">
+        <v>54</v>
+      </c>
+      <c r="AA5" s="1" t="s">
+        <v>23</v>
+      </c>
+      <c r="AB5" s="1" t="s">
+        <v>55</v>
+      </c>
+      <c r="AC5" s="1" t="s">
+        <v>41</v>
+      </c>
+      <c r="AD5" s="1" t="s">
+        <v>27</v>
+      </c>
+      <c r="AE5" s="1" t="s">
+        <v>82</v>
+      </c>
+      <c r="AK5" s="1" t="s">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="6" spans="1:37" x14ac:dyDescent="0.25">
+      <c r="A6" s="1" t="s">
+        <v>46</v>
+      </c>
+      <c r="B6" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="C6" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="D6" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="E6" s="1" t="s">
+        <v>70</v>
+      </c>
+      <c r="F6" s="1"/>
+      <c r="G6" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="H6" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="I6" s="1" t="s">
+        <v>12</v>
+      </c>
+      <c r="AE6" s="1" t="s">
+        <v>82</v>
+      </c>
+      <c r="AK6" s="1" t="s">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="7" spans="1:37" x14ac:dyDescent="0.25">
+      <c r="A7" s="1" t="s">
+        <v>48</v>
+      </c>
+      <c r="B7" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="C7" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="D7" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="E7" s="1" t="s">
+        <v>70</v>
+      </c>
+      <c r="F7" s="1"/>
+      <c r="G7" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="H7" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="I7" s="1" t="s">
+        <v>12</v>
+      </c>
+      <c r="AE7" s="1" t="s">
+        <v>90</v>
+      </c>
+      <c r="AF7" s="1" t="s">
+        <v>83</v>
+      </c>
+      <c r="AG7" s="1" t="s">
+        <v>84</v>
+      </c>
+      <c r="AH7" s="1" t="s">
+        <v>89</v>
+      </c>
+      <c r="AI7" s="1" t="s">
+        <v>87</v>
+      </c>
+      <c r="AJ7" s="1" t="s">
+        <v>88</v>
+      </c>
+    </row>
+    <row r="8" spans="1:37" x14ac:dyDescent="0.25">
+      <c r="A8" s="1" t="s">
+        <v>103</v>
+      </c>
+      <c r="B8" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="C8" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="D8" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="E8" s="1" t="s">
+        <v>102</v>
+      </c>
+      <c r="F8" s="1"/>
+      <c r="G8" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="H8" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="I8" s="1" t="s">
+        <v>12</v>
+      </c>
+      <c r="J8" s="1"/>
+      <c r="K8" s="1"/>
+      <c r="L8" s="1" t="s">
+        <v>20</v>
+      </c>
+      <c r="O8" s="1" t="s">
+        <v>40</v>
+      </c>
+      <c r="P8" s="1" t="s">
+        <v>65</v>
+      </c>
+      <c r="Q8" s="1" t="s">
+        <v>49</v>
+      </c>
+      <c r="R8" s="1" t="s">
+        <v>50</v>
+      </c>
+      <c r="S8" s="1" t="s">
+        <v>23</v>
+      </c>
+      <c r="T8" s="1" t="s">
+        <v>51</v>
+      </c>
+      <c r="U8" s="1" t="s">
+        <v>26</v>
+      </c>
+      <c r="V8" s="1" t="s">
+        <v>27</v>
+      </c>
+      <c r="W8" s="1" t="s">
+        <v>40</v>
+      </c>
+      <c r="X8" s="1" t="s">
+        <v>52</v>
+      </c>
+      <c r="Y8" s="1" t="s">
+        <v>53</v>
+      </c>
+      <c r="Z8" s="2" t="s">
+        <v>54</v>
+      </c>
+      <c r="AA8" s="1" t="s">
+        <v>23</v>
+      </c>
+      <c r="AB8" s="1" t="s">
+        <v>55</v>
+      </c>
+      <c r="AC8" s="1" t="s">
+        <v>41</v>
+      </c>
+      <c r="AD8" s="1" t="s">
+        <v>27</v>
+      </c>
+      <c r="AE8" s="1" t="s">
+        <v>82</v>
+      </c>
+      <c r="AJ8" s="1"/>
+      <c r="AK8" s="1" t="s">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="9" spans="1:37" x14ac:dyDescent="0.25">
+      <c r="A9" s="1" t="s">
+        <v>96</v>
+      </c>
+      <c r="B9" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="C9" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="D9" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="E9" s="1" t="s">
+        <v>70</v>
+      </c>
+      <c r="F9" s="1"/>
+      <c r="G9" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="H9" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="I9" s="1" t="s">
+        <v>12</v>
+      </c>
+      <c r="AE9" s="1" t="s">
+        <v>98</v>
+      </c>
+    </row>
+    <row r="10" spans="1:37" x14ac:dyDescent="0.25">
+      <c r="A10" s="1" t="s">
+        <v>76</v>
+      </c>
+      <c r="B10" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="C10" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="D10" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="E10" s="1" t="s">
+        <v>72</v>
+      </c>
+      <c r="F10" s="2" t="s">
+        <v>105</v>
+      </c>
+      <c r="G10" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="H10" s="1" t="s">
+        <v>77</v>
+      </c>
+      <c r="I10" s="1" t="s">
+        <v>12</v>
+      </c>
+      <c r="J10" s="1"/>
+      <c r="K10" s="1"/>
+      <c r="L10" s="1" t="s">
+        <v>20</v>
+      </c>
+      <c r="O10" s="1" t="s">
+        <v>40</v>
+      </c>
+      <c r="P10" s="1" t="s">
+        <v>65</v>
+      </c>
+      <c r="Q10" s="1" t="s">
+        <v>49</v>
+      </c>
+      <c r="R10" s="1" t="s">
+        <v>50</v>
+      </c>
+      <c r="S10" s="1" t="s">
+        <v>23</v>
+      </c>
+      <c r="T10" s="1" t="s">
+        <v>51</v>
+      </c>
+      <c r="U10" s="1" t="s">
+        <v>26</v>
+      </c>
+      <c r="V10" s="1" t="s">
+        <v>27</v>
+      </c>
+      <c r="W10" s="1" t="s">
+        <v>40</v>
+      </c>
+      <c r="X10" s="1" t="s">
+        <v>52</v>
+      </c>
+      <c r="Y10" s="1" t="s">
+        <v>53</v>
+      </c>
+      <c r="Z10" s="2" t="s">
+        <v>54</v>
+      </c>
+      <c r="AA10" s="1" t="s">
+        <v>23</v>
+      </c>
+      <c r="AB10" s="1" t="s">
+        <v>55</v>
+      </c>
+      <c r="AC10" s="1" t="s">
+        <v>41</v>
+      </c>
+      <c r="AD10" s="1" t="s">
+        <v>27</v>
+      </c>
+      <c r="AE10" s="1" t="s">
+        <v>90</v>
+      </c>
+      <c r="AF10" s="1" t="s">
+        <v>83</v>
+      </c>
+      <c r="AG10" s="1" t="s">
+        <v>84</v>
+      </c>
+      <c r="AH10" s="1" t="s">
+        <v>89</v>
+      </c>
+      <c r="AI10" s="1" t="s">
+        <v>87</v>
+      </c>
+      <c r="AJ10" s="1" t="s">
+        <v>88</v>
+      </c>
+    </row>
+    <row r="11" spans="1:37" x14ac:dyDescent="0.25">
+      <c r="A11" s="1" t="s">
+        <v>97</v>
+      </c>
+      <c r="B11" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="C11" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="D11" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="E11" s="1" t="s">
+        <v>72</v>
+      </c>
+      <c r="F11" s="2" t="s">
+        <v>105</v>
+      </c>
+      <c r="G11" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="H11" s="1" t="s">
+        <v>77</v>
+      </c>
+      <c r="I11" s="1" t="s">
+        <v>12</v>
+      </c>
+      <c r="J11" s="1"/>
+      <c r="K11" s="1"/>
+      <c r="L11" s="1" t="s">
+        <v>20</v>
+      </c>
+      <c r="O11" s="1" t="s">
+        <v>40</v>
+      </c>
+      <c r="P11" s="1" t="s">
+        <v>65</v>
+      </c>
+      <c r="Q11" s="1" t="s">
+        <v>49</v>
+      </c>
+      <c r="R11" s="1" t="s">
+        <v>50</v>
+      </c>
+      <c r="S11" s="1" t="s">
+        <v>23</v>
+      </c>
+      <c r="T11" s="1" t="s">
+        <v>51</v>
+      </c>
+      <c r="U11" s="1" t="s">
+        <v>26</v>
+      </c>
+      <c r="V11" s="1" t="s">
+        <v>27</v>
+      </c>
+      <c r="W11" s="1" t="s">
+        <v>40</v>
+      </c>
+      <c r="X11" s="1" t="s">
+        <v>52</v>
+      </c>
+      <c r="Y11" s="1" t="s">
+        <v>53</v>
+      </c>
+      <c r="Z11" s="2" t="s">
+        <v>54</v>
+      </c>
+      <c r="AA11" s="1" t="s">
+        <v>23</v>
+      </c>
+      <c r="AB11" s="1" t="s">
+        <v>55</v>
+      </c>
+      <c r="AC11" s="1" t="s">
+        <v>41</v>
+      </c>
+      <c r="AD11" s="1" t="s">
+        <v>27</v>
+      </c>
+      <c r="AE11" s="1" t="s">
+        <v>82</v>
+      </c>
+      <c r="AK11" s="1" t="s">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="12" spans="1:37" x14ac:dyDescent="0.25">
+      <c r="A12" s="1" t="s">
+        <v>107</v>
+      </c>
+      <c r="B12" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="C12" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="D12" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="E12" s="1" t="s">
+        <v>102</v>
+      </c>
+      <c r="F12" s="2" t="s">
+        <v>106</v>
+      </c>
+      <c r="G12" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="H12" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="I12" s="1" t="s">
+        <v>12</v>
+      </c>
+      <c r="J12" s="1"/>
+      <c r="K12" s="1"/>
+      <c r="L12" s="1" t="s">
+        <v>20</v>
+      </c>
+      <c r="O12" s="1" t="s">
+        <v>40</v>
+      </c>
+      <c r="P12" s="1" t="s">
+        <v>65</v>
+      </c>
+      <c r="Q12" s="1" t="s">
+        <v>49</v>
+      </c>
+      <c r="R12" s="1" t="s">
+        <v>50</v>
+      </c>
+      <c r="S12" s="1" t="s">
+        <v>23</v>
+      </c>
+      <c r="T12" s="1" t="s">
+        <v>51</v>
+      </c>
+      <c r="U12" s="1" t="s">
+        <v>26</v>
+      </c>
+      <c r="V12" s="1" t="s">
+        <v>27</v>
+      </c>
+      <c r="W12" s="1" t="s">
+        <v>40</v>
+      </c>
+      <c r="X12" s="1" t="s">
+        <v>52</v>
+      </c>
+      <c r="Y12" s="1" t="s">
+        <v>53</v>
+      </c>
+      <c r="Z12" s="2" t="s">
+        <v>54</v>
+      </c>
+      <c r="AA12" s="1" t="s">
+        <v>23</v>
+      </c>
+      <c r="AB12" s="1" t="s">
+        <v>55</v>
+      </c>
+      <c r="AC12" s="1" t="s">
+        <v>41</v>
+      </c>
+      <c r="AD12" s="1" t="s">
+        <v>27</v>
+      </c>
+      <c r="AE12" s="1" t="s">
+        <v>90</v>
+      </c>
+      <c r="AF12" s="1" t="s">
+        <v>83</v>
+      </c>
+      <c r="AG12" s="1" t="s">
+        <v>84</v>
+      </c>
+      <c r="AH12" s="1" t="s">
+        <v>89</v>
+      </c>
+      <c r="AI12" s="1" t="s">
+        <v>87</v>
+      </c>
+      <c r="AJ12" s="1" t="s">
+        <v>88</v>
+      </c>
+    </row>
+    <row r="13" spans="1:37" x14ac:dyDescent="0.25">
+      <c r="A13" s="1" t="s">
+        <v>108</v>
+      </c>
+      <c r="B13" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="C13" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="D13" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="E13" s="1" t="s">
+        <v>102</v>
+      </c>
+      <c r="F13" s="2" t="s">
+        <v>106</v>
+      </c>
+      <c r="G13" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="H13" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="I13" s="1" t="s">
+        <v>12</v>
+      </c>
+      <c r="J13" s="1"/>
+      <c r="K13" s="1"/>
+      <c r="L13" s="1" t="s">
+        <v>20</v>
+      </c>
+      <c r="O13" s="1" t="s">
+        <v>40</v>
+      </c>
+      <c r="P13" s="1" t="s">
+        <v>65</v>
+      </c>
+      <c r="Q13" s="1" t="s">
+        <v>49</v>
+      </c>
+      <c r="R13" s="1" t="s">
+        <v>50</v>
+      </c>
+      <c r="S13" s="1" t="s">
+        <v>23</v>
+      </c>
+      <c r="T13" s="1" t="s">
+        <v>51</v>
+      </c>
+      <c r="U13" s="1" t="s">
+        <v>26</v>
+      </c>
+      <c r="V13" s="1" t="s">
+        <v>27</v>
+      </c>
+      <c r="W13" s="1" t="s">
+        <v>40</v>
+      </c>
+      <c r="X13" s="1" t="s">
+        <v>52</v>
+      </c>
+      <c r="Y13" s="1" t="s">
+        <v>53</v>
+      </c>
+      <c r="Z13" s="2" t="s">
+        <v>54</v>
+      </c>
+      <c r="AA13" s="1" t="s">
+        <v>23</v>
+      </c>
+      <c r="AB13" s="1" t="s">
+        <v>55</v>
+      </c>
+      <c r="AC13" s="1" t="s">
+        <v>41</v>
+      </c>
+      <c r="AD13" s="1" t="s">
+        <v>27</v>
+      </c>
+      <c r="AE13" s="1" t="s">
+        <v>82</v>
+      </c>
+      <c r="AK13" s="1" t="s">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="14" spans="1:37" x14ac:dyDescent="0.25">
+      <c r="A14" s="1" t="s">
+        <v>114</v>
+      </c>
+      <c r="B14" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="C14" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="D14" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="E14" s="1" t="s">
+        <v>70</v>
+      </c>
+      <c r="F14" s="2" t="s">
+        <v>71</v>
+      </c>
+      <c r="G14" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="H14" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="I14" s="1" t="s">
+        <v>12</v>
+      </c>
+      <c r="AE14" s="1" t="s">
+        <v>82</v>
+      </c>
+      <c r="AK14" s="1" t="s">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="15" spans="1:37" x14ac:dyDescent="0.25">
+      <c r="A15" s="1" t="s">
+        <v>109</v>
+      </c>
+      <c r="B15" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="C15" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="D15" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="E15" s="1" t="s">
+        <v>70</v>
+      </c>
+      <c r="F15" s="2" t="s">
+        <v>71</v>
+      </c>
+      <c r="G15" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="H15" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="I15" s="1" t="s">
+        <v>12</v>
+      </c>
+      <c r="AE15" s="1" t="s">
+        <v>90</v>
+      </c>
+      <c r="AF15" s="1" t="s">
+        <v>83</v>
+      </c>
+      <c r="AG15" s="1" t="s">
+        <v>84</v>
+      </c>
+      <c r="AH15" s="1" t="s">
+        <v>89</v>
+      </c>
+      <c r="AI15" s="1" t="s">
+        <v>87</v>
+      </c>
+      <c r="AJ15" s="1" t="s">
+        <v>88</v>
+      </c>
+    </row>
+    <row r="16" spans="1:37" x14ac:dyDescent="0.25">
+      <c r="A16" s="1" t="s">
+        <v>115</v>
+      </c>
+      <c r="B16" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="C16" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="D16" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="E16" s="1" t="s">
+        <v>102</v>
+      </c>
+      <c r="F16" s="2" t="s">
+        <v>106</v>
+      </c>
+      <c r="G16" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="H16" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="I16" s="1" t="s">
+        <v>12</v>
+      </c>
+      <c r="J16" s="1"/>
+      <c r="K16" s="1"/>
+      <c r="L16" s="1" t="s">
+        <v>20</v>
+      </c>
+      <c r="O16" s="1" t="s">
+        <v>40</v>
+      </c>
+      <c r="P16" s="1" t="s">
+        <v>65</v>
+      </c>
+      <c r="Q16" s="1" t="s">
+        <v>49</v>
+      </c>
+      <c r="R16" s="1" t="s">
+        <v>50</v>
+      </c>
+      <c r="S16" s="1" t="s">
+        <v>23</v>
+      </c>
+      <c r="T16" s="1" t="s">
+        <v>51</v>
+      </c>
+      <c r="U16" s="1" t="s">
+        <v>26</v>
+      </c>
+      <c r="V16" s="1" t="s">
+        <v>27</v>
+      </c>
+      <c r="W16" s="1" t="s">
+        <v>40</v>
+      </c>
+      <c r="X16" s="1" t="s">
+        <v>52</v>
+      </c>
+      <c r="Y16" s="1" t="s">
+        <v>53</v>
+      </c>
+      <c r="Z16" s="2" t="s">
+        <v>54</v>
+      </c>
+      <c r="AA16" s="1" t="s">
+        <v>23</v>
+      </c>
+      <c r="AB16" s="1" t="s">
+        <v>55</v>
+      </c>
+      <c r="AC16" s="1" t="s">
+        <v>41</v>
+      </c>
+      <c r="AD16" s="1" t="s">
+        <v>27</v>
+      </c>
+      <c r="AE16" s="1" t="s">
+        <v>82</v>
+      </c>
+      <c r="AJ16" s="1"/>
+      <c r="AK16" s="1" t="s">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="17" spans="1:37" x14ac:dyDescent="0.25">
+      <c r="A17" s="1" t="s">
+        <v>116</v>
+      </c>
+      <c r="B17" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="C17" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="D17" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="E17" s="1" t="s">
+        <v>70</v>
+      </c>
+      <c r="F17" s="2" t="s">
+        <v>73</v>
+      </c>
+      <c r="G17" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="H17" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="I17" s="1" t="s">
+        <v>12</v>
+      </c>
+      <c r="AE17" s="1" t="s">
+        <v>98</v>
+      </c>
+    </row>
+    <row r="18" spans="1:37" x14ac:dyDescent="0.25">
+      <c r="A18" s="1" t="s">
+        <v>117</v>
+      </c>
+      <c r="B18" s="1" t="s">
+        <v>47</v>
+      </c>
+      <c r="C18" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="D18" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="E18" s="1" t="s">
+        <v>72</v>
+      </c>
+      <c r="F18" s="1"/>
+      <c r="G18" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="H18" s="1" t="s">
+        <v>77</v>
+      </c>
+      <c r="I18" s="1" t="s">
+        <v>12</v>
+      </c>
+      <c r="J18" s="1" t="s">
+        <v>45</v>
+      </c>
+      <c r="K18" s="1" t="s">
+        <v>105</v>
+      </c>
+      <c r="O18" s="1" t="s">
+        <v>40</v>
+      </c>
+      <c r="P18" s="1" t="s">
+        <v>65</v>
+      </c>
+      <c r="Q18" s="1" t="s">
+        <v>49</v>
+      </c>
+      <c r="R18" s="1" t="s">
+        <v>50</v>
+      </c>
+      <c r="S18" s="1" t="s">
+        <v>23</v>
+      </c>
+      <c r="T18" s="1" t="s">
+        <v>51</v>
+      </c>
+      <c r="U18" s="1" t="s">
+        <v>26</v>
+      </c>
+      <c r="V18" s="1" t="s">
+        <v>27</v>
+      </c>
+      <c r="W18" s="1" t="s">
+        <v>40</v>
+      </c>
+      <c r="X18" s="1" t="s">
+        <v>52</v>
+      </c>
+      <c r="Y18" s="1" t="s">
+        <v>53</v>
+      </c>
+      <c r="Z18" s="2" t="s">
+        <v>54</v>
+      </c>
+      <c r="AA18" s="1" t="s">
+        <v>23</v>
+      </c>
+      <c r="AB18" s="1" t="s">
+        <v>55</v>
+      </c>
+      <c r="AC18" s="1" t="s">
+        <v>41</v>
+      </c>
+      <c r="AD18" s="1" t="s">
+        <v>27</v>
+      </c>
+      <c r="AE18" s="1" t="s">
+        <v>90</v>
+      </c>
+      <c r="AF18" s="1" t="s">
+        <v>83</v>
+      </c>
+      <c r="AG18" s="1" t="s">
+        <v>84</v>
+      </c>
+      <c r="AH18" s="1" t="s">
+        <v>89</v>
+      </c>
+      <c r="AI18" s="1" t="s">
+        <v>87</v>
+      </c>
+      <c r="AJ18" s="1" t="s">
+        <v>88</v>
+      </c>
+    </row>
+    <row r="19" spans="1:37" x14ac:dyDescent="0.25">
+      <c r="A19" s="1" t="s">
+        <v>110</v>
+      </c>
+      <c r="B19" s="1" t="s">
+        <v>47</v>
+      </c>
+      <c r="C19" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="D19" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="E19" s="1" t="s">
+        <v>72</v>
+      </c>
+      <c r="F19" s="1"/>
+      <c r="G19" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="H19" s="1" t="s">
+        <v>77</v>
+      </c>
+      <c r="I19" s="1" t="s">
+        <v>12</v>
+      </c>
+      <c r="J19" s="1" t="s">
+        <v>45</v>
+      </c>
+      <c r="K19" s="1" t="s">
+        <v>105</v>
+      </c>
+      <c r="L19" s="1" t="s">
+        <v>20</v>
+      </c>
+      <c r="O19" s="1" t="s">
+        <v>40</v>
+      </c>
+      <c r="P19" s="1" t="s">
+        <v>65</v>
+      </c>
+      <c r="Q19" s="1" t="s">
+        <v>49</v>
+      </c>
+      <c r="R19" s="1" t="s">
+        <v>50</v>
+      </c>
+      <c r="S19" s="1" t="s">
+        <v>23</v>
+      </c>
+      <c r="T19" s="1" t="s">
+        <v>51</v>
+      </c>
+      <c r="U19" s="1" t="s">
+        <v>26</v>
+      </c>
+      <c r="V19" s="1" t="s">
+        <v>27</v>
+      </c>
+      <c r="W19" s="1" t="s">
+        <v>40</v>
+      </c>
+      <c r="X19" s="1" t="s">
+        <v>52</v>
+      </c>
+      <c r="Y19" s="1" t="s">
+        <v>53</v>
+      </c>
+      <c r="Z19" s="2" t="s">
+        <v>54</v>
+      </c>
+      <c r="AA19" s="1" t="s">
+        <v>23</v>
+      </c>
+      <c r="AB19" s="1" t="s">
+        <v>55</v>
+      </c>
+      <c r="AC19" s="1" t="s">
+        <v>41</v>
+      </c>
+      <c r="AD19" s="1" t="s">
+        <v>27</v>
+      </c>
+      <c r="AE19" s="1" t="s">
+        <v>82</v>
+      </c>
+      <c r="AK19" s="1" t="s">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="20" spans="1:37" x14ac:dyDescent="0.25">
+      <c r="A20" s="1" t="s">
+        <v>111</v>
+      </c>
+      <c r="B20" s="1" t="s">
+        <v>47</v>
+      </c>
+      <c r="C20" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="D20" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="E20" s="1" t="s">
+        <v>102</v>
+      </c>
+      <c r="F20" s="1"/>
+      <c r="G20" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="H20" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="I20" s="1" t="s">
+        <v>12</v>
+      </c>
+      <c r="J20" s="1" t="s">
+        <v>45</v>
+      </c>
+      <c r="K20" s="1" t="s">
+        <v>106</v>
+      </c>
+      <c r="L20" s="1" t="s">
+        <v>20</v>
+      </c>
+      <c r="O20" s="1" t="s">
+        <v>40</v>
+      </c>
+      <c r="P20" s="1" t="s">
+        <v>65</v>
+      </c>
+      <c r="Q20" s="1" t="s">
+        <v>49</v>
+      </c>
+      <c r="R20" s="1" t="s">
+        <v>50</v>
+      </c>
+      <c r="S20" s="1" t="s">
+        <v>23</v>
+      </c>
+      <c r="T20" s="1" t="s">
+        <v>51</v>
+      </c>
+      <c r="U20" s="1" t="s">
+        <v>26</v>
+      </c>
+      <c r="V20" s="1" t="s">
+        <v>27</v>
+      </c>
+      <c r="W20" s="1" t="s">
+        <v>40</v>
+      </c>
+      <c r="X20" s="1" t="s">
+        <v>52</v>
+      </c>
+      <c r="Y20" s="1" t="s">
+        <v>53</v>
+      </c>
+      <c r="Z20" s="2" t="s">
+        <v>54</v>
+      </c>
+      <c r="AA20" s="1" t="s">
+        <v>23</v>
+      </c>
+      <c r="AB20" s="1" t="s">
+        <v>55</v>
+      </c>
+      <c r="AC20" s="1" t="s">
+        <v>41</v>
+      </c>
+      <c r="AD20" s="1" t="s">
+        <v>27</v>
+      </c>
+      <c r="AE20" s="1" t="s">
+        <v>90</v>
+      </c>
+      <c r="AF20" s="1" t="s">
+        <v>83</v>
+      </c>
+      <c r="AG20" s="1" t="s">
+        <v>84</v>
+      </c>
+      <c r="AH20" s="1" t="s">
+        <v>89</v>
+      </c>
+      <c r="AI20" s="1" t="s">
+        <v>87</v>
+      </c>
+      <c r="AJ20" s="1" t="s">
+        <v>88</v>
+      </c>
+    </row>
+    <row r="21" spans="1:37" x14ac:dyDescent="0.25">
+      <c r="A21" s="1" t="s">
+        <v>112</v>
+      </c>
+      <c r="B21" s="1" t="s">
+        <v>47</v>
+      </c>
+      <c r="C21" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="D21" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="E21" s="1" t="s">
+        <v>102</v>
+      </c>
+      <c r="F21" s="1"/>
+      <c r="G21" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="H21" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="I21" s="1" t="s">
+        <v>12</v>
+      </c>
+      <c r="J21" s="1" t="s">
+        <v>45</v>
+      </c>
+      <c r="K21" s="1" t="s">
+        <v>106</v>
+      </c>
+      <c r="L21" s="1" t="s">
+        <v>20</v>
+      </c>
+      <c r="O21" s="1" t="s">
+        <v>40</v>
+      </c>
+      <c r="P21" s="1" t="s">
+        <v>65</v>
+      </c>
+      <c r="Q21" s="1" t="s">
+        <v>49</v>
+      </c>
+      <c r="R21" s="1" t="s">
+        <v>50</v>
+      </c>
+      <c r="S21" s="1" t="s">
+        <v>23</v>
+      </c>
+      <c r="T21" s="1" t="s">
+        <v>51</v>
+      </c>
+      <c r="U21" s="1" t="s">
+        <v>26</v>
+      </c>
+      <c r="V21" s="1" t="s">
+        <v>27</v>
+      </c>
+      <c r="W21" s="1" t="s">
+        <v>40</v>
+      </c>
+      <c r="X21" s="1" t="s">
+        <v>52</v>
+      </c>
+      <c r="Y21" s="1" t="s">
+        <v>53</v>
+      </c>
+      <c r="Z21" s="2" t="s">
+        <v>54</v>
+      </c>
+      <c r="AA21" s="1" t="s">
+        <v>23</v>
+      </c>
+      <c r="AB21" s="1" t="s">
+        <v>55</v>
+      </c>
+      <c r="AC21" s="1" t="s">
+        <v>41</v>
+      </c>
+      <c r="AD21" s="1" t="s">
+        <v>27</v>
+      </c>
+      <c r="AE21" s="1" t="s">
+        <v>82</v>
+      </c>
+      <c r="AK21" s="1" t="s">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="22" spans="1:37" x14ac:dyDescent="0.25">
+      <c r="A22" s="1" t="s">
+        <v>118</v>
+      </c>
+      <c r="B22" s="1" t="s">
+        <v>47</v>
+      </c>
+      <c r="C22" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="D22" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="E22" s="1" t="s">
+        <v>70</v>
+      </c>
+      <c r="F22" s="1"/>
+      <c r="G22" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="H22" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="I22" s="1" t="s">
+        <v>12</v>
+      </c>
+      <c r="J22" s="1" t="s">
+        <v>45</v>
+      </c>
+      <c r="K22" s="1" t="s">
+        <v>71</v>
+      </c>
+      <c r="AE22" s="1" t="s">
+        <v>82</v>
+      </c>
+      <c r="AK22" s="1" t="s">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="23" spans="1:37" x14ac:dyDescent="0.25">
+      <c r="A23" s="1" t="s">
+        <v>113</v>
+      </c>
+      <c r="B23" s="1" t="s">
+        <v>47</v>
+      </c>
+      <c r="C23" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="D23" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="E23" s="1" t="s">
+        <v>70</v>
+      </c>
+      <c r="F23" s="1"/>
+      <c r="G23" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="H23" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="I23" s="1" t="s">
+        <v>12</v>
+      </c>
+      <c r="J23" s="1" t="s">
+        <v>45</v>
+      </c>
+      <c r="K23" s="1" t="s">
+        <v>71</v>
+      </c>
+      <c r="AE23" s="1" t="s">
+        <v>90</v>
+      </c>
+      <c r="AF23" s="1" t="s">
+        <v>83</v>
+      </c>
+      <c r="AG23" s="1" t="s">
+        <v>84</v>
+      </c>
+      <c r="AH23" s="1" t="s">
+        <v>89</v>
+      </c>
+      <c r="AI23" s="1" t="s">
+        <v>87</v>
+      </c>
+      <c r="AJ23" s="1" t="s">
+        <v>88</v>
+      </c>
+    </row>
+    <row r="24" spans="1:37" x14ac:dyDescent="0.25">
+      <c r="A24" s="1" t="s">
+        <v>119</v>
+      </c>
+      <c r="B24" s="1" t="s">
+        <v>47</v>
+      </c>
+      <c r="C24" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="D24" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="E24" s="1" t="s">
+        <v>102</v>
+      </c>
+      <c r="F24" s="1"/>
+      <c r="G24" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="H24" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="I24" s="1" t="s">
+        <v>12</v>
+      </c>
+      <c r="J24" s="1" t="s">
+        <v>45</v>
+      </c>
+      <c r="K24" s="1" t="s">
+        <v>106</v>
+      </c>
+      <c r="L24" s="1" t="s">
+        <v>20</v>
+      </c>
+      <c r="O24" s="1" t="s">
+        <v>40</v>
+      </c>
+      <c r="P24" s="1" t="s">
+        <v>65</v>
+      </c>
+      <c r="Q24" s="1" t="s">
+        <v>49</v>
+      </c>
+      <c r="R24" s="1" t="s">
+        <v>50</v>
+      </c>
+      <c r="S24" s="1" t="s">
+        <v>23</v>
+      </c>
+      <c r="T24" s="1" t="s">
+        <v>51</v>
+      </c>
+      <c r="U24" s="1" t="s">
+        <v>26</v>
+      </c>
+      <c r="V24" s="1" t="s">
+        <v>27</v>
+      </c>
+      <c r="W24" s="1" t="s">
+        <v>40</v>
+      </c>
+      <c r="X24" s="1" t="s">
+        <v>52</v>
+      </c>
+      <c r="Y24" s="1" t="s">
+        <v>53</v>
+      </c>
+      <c r="Z24" s="2" t="s">
+        <v>54</v>
+      </c>
+      <c r="AA24" s="1" t="s">
+        <v>23</v>
+      </c>
+      <c r="AB24" s="1" t="s">
+        <v>55</v>
+      </c>
+      <c r="AC24" s="1" t="s">
+        <v>41</v>
+      </c>
+      <c r="AD24" s="1" t="s">
+        <v>27</v>
+      </c>
+      <c r="AE24" s="1" t="s">
+        <v>82</v>
+      </c>
+      <c r="AJ24" s="1"/>
+      <c r="AK24" s="1" t="s">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="25" spans="1:37" x14ac:dyDescent="0.25">
+      <c r="A25" s="1" t="s">
+        <v>120</v>
+      </c>
+      <c r="B25" s="1" t="s">
+        <v>47</v>
+      </c>
+      <c r="C25" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="D25" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="E25" s="1" t="s">
+        <v>70</v>
+      </c>
+      <c r="F25" s="1"/>
+      <c r="G25" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="H25" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="I25" s="1" t="s">
+        <v>12</v>
+      </c>
+      <c r="J25" s="1" t="s">
+        <v>45</v>
+      </c>
+      <c r="K25" s="1" t="s">
+        <v>71</v>
+      </c>
+      <c r="AE25" s="1" t="s">
+        <v>98</v>
       </c>
     </row>
   </sheetData>
@@ -850,178 +2671,108 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{2CCE6EC1-6C99-4FA8-9E5E-FE50AE294D93}">
-  <dimension ref="A1:AD7"/>
+  <dimension ref="A1:AK37"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <cols>
+    <col min="1" max="1" width="83" customWidth="1"/>
+    <col min="10" max="10" width="29.28515625" customWidth="1"/>
+  </cols>
   <sheetData>
-    <row r="1" spans="1:30" x14ac:dyDescent="0.25">
-      <c r="A1" s="1" t="s">
-        <v>61</v>
+    <row r="1" spans="1:36" x14ac:dyDescent="0.25">
+      <c r="A1" t="s">
+        <v>0</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>9</v>
+        <v>1</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>16</v>
+        <v>2</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>17</v>
+        <v>3</v>
       </c>
       <c r="E1" s="1" t="s">
-        <v>48</v>
+        <v>4</v>
       </c>
       <c r="F1" s="1" t="s">
-        <v>70</v>
+        <v>7</v>
       </c>
       <c r="G1" s="1" t="s">
-        <v>19</v>
+        <v>5</v>
       </c>
       <c r="H1" s="1" t="s">
-        <v>11</v>
+        <v>8</v>
       </c>
       <c r="I1" s="1" t="s">
-        <v>12</v>
-      </c>
-      <c r="J1" s="1"/>
-      <c r="K1" s="1"/>
+        <v>6</v>
+      </c>
+      <c r="J1" s="1" t="s">
+        <v>43</v>
+      </c>
+      <c r="K1" s="1" t="s">
+        <v>44</v>
+      </c>
       <c r="L1" s="1" t="s">
-        <v>20</v>
+        <v>13</v>
+      </c>
+      <c r="M1" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="N1" s="1" t="s">
+        <v>15</v>
       </c>
       <c r="O1" s="1" t="s">
-        <v>40</v>
+        <v>34</v>
       </c>
       <c r="P1" s="1" t="s">
-        <v>74</v>
+        <v>35</v>
       </c>
       <c r="Q1" s="1" t="s">
-        <v>52</v>
+        <v>36</v>
       </c>
       <c r="R1" s="1" t="s">
-        <v>53</v>
+        <v>21</v>
       </c>
       <c r="S1" s="1" t="s">
-        <v>23</v>
+        <v>33</v>
       </c>
       <c r="T1" s="1" t="s">
-        <v>54</v>
+        <v>30</v>
       </c>
       <c r="U1" s="1" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="V1" s="1" t="s">
-        <v>27</v>
+        <v>31</v>
       </c>
       <c r="W1" s="1" t="s">
-        <v>40</v>
+        <v>37</v>
       </c>
       <c r="X1" s="1" t="s">
-        <v>55</v>
+        <v>38</v>
       </c>
       <c r="Y1" s="1" t="s">
-        <v>56</v>
-      </c>
-      <c r="Z1" s="2" t="s">
+        <v>39</v>
+      </c>
+      <c r="Z1" s="1" t="s">
+        <v>28</v>
+      </c>
+      <c r="AA1" s="1" t="s">
+        <v>22</v>
+      </c>
+      <c r="AB1" s="1" t="s">
+        <v>24</v>
+      </c>
+      <c r="AC1" s="1" t="s">
+        <v>29</v>
+      </c>
+      <c r="AD1" t="s">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="3" spans="1:36" x14ac:dyDescent="0.25">
+      <c r="A3" s="1" t="s">
         <v>57</v>
-      </c>
-      <c r="AA1" s="1" t="s">
-        <v>23</v>
-      </c>
-      <c r="AB1" s="1" t="s">
-        <v>58</v>
-      </c>
-      <c r="AC1" s="1" t="s">
-        <v>41</v>
-      </c>
-      <c r="AD1" s="1" t="s">
-        <v>27</v>
-      </c>
-    </row>
-    <row r="2" spans="1:30" x14ac:dyDescent="0.25">
-      <c r="A2" s="1" t="s">
-        <v>49</v>
-      </c>
-      <c r="B2" s="1" t="s">
-        <v>47</v>
-      </c>
-      <c r="C2" s="1" t="s">
-        <v>16</v>
-      </c>
-      <c r="D2" s="1" t="s">
-        <v>17</v>
-      </c>
-      <c r="E2" s="1" t="s">
-        <v>48</v>
-      </c>
-      <c r="F2" s="1"/>
-      <c r="G2" s="1" t="s">
-        <v>19</v>
-      </c>
-      <c r="H2" s="1" t="s">
-        <v>11</v>
-      </c>
-      <c r="I2" s="1" t="s">
-        <v>12</v>
-      </c>
-      <c r="J2" s="1" t="s">
-        <v>45</v>
-      </c>
-      <c r="K2" s="1" t="s">
-        <v>48</v>
-      </c>
-      <c r="L2" s="1" t="s">
-        <v>20</v>
-      </c>
-      <c r="O2" s="1" t="s">
-        <v>40</v>
-      </c>
-      <c r="P2" s="1" t="s">
-        <v>75</v>
-      </c>
-      <c r="Q2" s="1" t="s">
-        <v>52</v>
-      </c>
-      <c r="R2" s="1" t="s">
-        <v>53</v>
-      </c>
-      <c r="S2" s="1" t="s">
-        <v>23</v>
-      </c>
-      <c r="T2" s="1" t="s">
-        <v>54</v>
-      </c>
-      <c r="U2" s="1" t="s">
-        <v>26</v>
-      </c>
-      <c r="V2" s="1" t="s">
-        <v>27</v>
-      </c>
-      <c r="W2" s="1" t="s">
-        <v>40</v>
-      </c>
-      <c r="X2" s="1" t="s">
-        <v>55</v>
-      </c>
-      <c r="Y2" s="1" t="s">
-        <v>56</v>
-      </c>
-      <c r="Z2" s="2" t="s">
-        <v>57</v>
-      </c>
-      <c r="AA2" s="1" t="s">
-        <v>23</v>
-      </c>
-      <c r="AB2" s="1" t="s">
-        <v>58</v>
-      </c>
-      <c r="AC2" s="1" t="s">
-        <v>41</v>
-      </c>
-      <c r="AD2" s="1" t="s">
-        <v>27</v>
-      </c>
-    </row>
-    <row r="3" spans="1:30" x14ac:dyDescent="0.25">
-      <c r="A3" s="1" t="s">
-        <v>59</v>
       </c>
       <c r="B3" s="1" t="s">
         <v>9</v>
@@ -1033,27 +2784,80 @@
         <v>17</v>
       </c>
       <c r="E3" s="1" t="s">
-        <v>70</v>
+        <v>67</v>
       </c>
       <c r="F3" s="1" t="s">
-        <v>71</v>
+        <v>68</v>
       </c>
       <c r="G3" s="1" t="s">
         <v>10</v>
       </c>
       <c r="H3" s="1" t="s">
-        <v>11</v>
+        <v>77</v>
       </c>
       <c r="I3" s="1" t="s">
         <v>12</v>
       </c>
-    </row>
-    <row r="4" spans="1:30" x14ac:dyDescent="0.25">
+      <c r="J3" s="1"/>
+      <c r="K3" s="1"/>
+      <c r="L3" s="1" t="s">
+        <v>20</v>
+      </c>
+      <c r="O3" s="1" t="s">
+        <v>40</v>
+      </c>
+      <c r="P3" s="1" t="s">
+        <v>65</v>
+      </c>
+      <c r="Q3" s="1" t="s">
+        <v>49</v>
+      </c>
+      <c r="R3" s="1" t="s">
+        <v>50</v>
+      </c>
+      <c r="S3" s="1" t="s">
+        <v>23</v>
+      </c>
+      <c r="T3" s="1" t="s">
+        <v>51</v>
+      </c>
+      <c r="U3" s="1" t="s">
+        <v>26</v>
+      </c>
+      <c r="V3" s="1" t="s">
+        <v>27</v>
+      </c>
+      <c r="W3" s="1" t="s">
+        <v>40</v>
+      </c>
+      <c r="X3" s="1" t="s">
+        <v>52</v>
+      </c>
+      <c r="Y3" s="1" t="s">
+        <v>53</v>
+      </c>
+      <c r="Z3" s="2" t="s">
+        <v>54</v>
+      </c>
+      <c r="AA3" s="1" t="s">
+        <v>23</v>
+      </c>
+      <c r="AB3" s="1" t="s">
+        <v>55</v>
+      </c>
+      <c r="AC3" s="1" t="s">
+        <v>41</v>
+      </c>
+      <c r="AD3" s="1" t="s">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="4" spans="1:36" x14ac:dyDescent="0.25">
       <c r="A4" s="1" t="s">
-        <v>46</v>
+        <v>74</v>
       </c>
       <c r="B4" s="1" t="s">
-        <v>18</v>
+        <v>9</v>
       </c>
       <c r="C4" s="1" t="s">
         <v>16</v>
@@ -1062,11 +2866,13 @@
         <v>17</v>
       </c>
       <c r="E4" s="1" t="s">
-        <v>70</v>
-      </c>
-      <c r="F4" s="1"/>
+        <v>67</v>
+      </c>
+      <c r="F4" s="1" t="s">
+        <v>68</v>
+      </c>
       <c r="G4" s="1" t="s">
-        <v>10</v>
+        <v>19</v>
       </c>
       <c r="H4" s="1" t="s">
         <v>11</v>
@@ -1076,10 +2882,61 @@
       </c>
       <c r="J4" s="1"/>
       <c r="K4" s="1"/>
-    </row>
-    <row r="5" spans="1:30" x14ac:dyDescent="0.25">
+      <c r="L4" s="1" t="s">
+        <v>20</v>
+      </c>
+      <c r="O4" s="1" t="s">
+        <v>40</v>
+      </c>
+      <c r="P4" s="1" t="s">
+        <v>65</v>
+      </c>
+      <c r="Q4" s="1" t="s">
+        <v>49</v>
+      </c>
+      <c r="R4" s="1" t="s">
+        <v>50</v>
+      </c>
+      <c r="S4" s="1" t="s">
+        <v>23</v>
+      </c>
+      <c r="T4" s="1" t="s">
+        <v>51</v>
+      </c>
+      <c r="U4" s="1" t="s">
+        <v>26</v>
+      </c>
+      <c r="V4" s="1" t="s">
+        <v>27</v>
+      </c>
+      <c r="W4" s="1" t="s">
+        <v>40</v>
+      </c>
+      <c r="X4" s="1" t="s">
+        <v>52</v>
+      </c>
+      <c r="Y4" s="1" t="s">
+        <v>53</v>
+      </c>
+      <c r="Z4" s="2" t="s">
+        <v>54</v>
+      </c>
+      <c r="AA4" s="1" t="s">
+        <v>23</v>
+      </c>
+      <c r="AB4" s="1" t="s">
+        <v>55</v>
+      </c>
+      <c r="AC4" s="1" t="s">
+        <v>41</v>
+      </c>
+      <c r="AD4" s="1" t="s">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="5" spans="1:36" x14ac:dyDescent="0.25">
       <c r="A5" s="1" t="s">
-        <v>50</v>
+        <v>56</v>
       </c>
       <c r="B5" s="1" t="s">
         <v>47</v>
@@ -1091,11 +2948,11 @@
         <v>17</v>
       </c>
       <c r="E5" s="1" t="s">
-        <v>48</v>
+        <v>71</v>
       </c>
       <c r="F5" s="1"/>
       <c r="G5" s="1" t="s">
-        <v>10</v>
+        <v>19</v>
       </c>
       <c r="H5" s="1" t="s">
         <v>11</v>
@@ -1107,15 +2964,66 @@
         <v>45</v>
       </c>
       <c r="K5" s="1" t="s">
-        <v>48</v>
-      </c>
-    </row>
-    <row r="6" spans="1:30" x14ac:dyDescent="0.25">
+        <v>72</v>
+      </c>
+      <c r="L5" s="1" t="s">
+        <v>20</v>
+      </c>
+      <c r="O5" s="1" t="s">
+        <v>40</v>
+      </c>
+      <c r="P5" s="1" t="s">
+        <v>66</v>
+      </c>
+      <c r="Q5" s="1" t="s">
+        <v>49</v>
+      </c>
+      <c r="R5" s="1" t="s">
+        <v>50</v>
+      </c>
+      <c r="S5" s="1" t="s">
+        <v>23</v>
+      </c>
+      <c r="T5" s="1" t="s">
+        <v>51</v>
+      </c>
+      <c r="U5" s="1" t="s">
+        <v>26</v>
+      </c>
+      <c r="V5" s="1" t="s">
+        <v>27</v>
+      </c>
+      <c r="W5" s="1" t="s">
+        <v>40</v>
+      </c>
+      <c r="X5" s="1" t="s">
+        <v>52</v>
+      </c>
+      <c r="Y5" s="1" t="s">
+        <v>53</v>
+      </c>
+      <c r="Z5" s="2" t="s">
+        <v>54</v>
+      </c>
+      <c r="AA5" s="1" t="s">
+        <v>23</v>
+      </c>
+      <c r="AB5" s="1" t="s">
+        <v>55</v>
+      </c>
+      <c r="AC5" s="1" t="s">
+        <v>41</v>
+      </c>
+      <c r="AD5" s="1" t="s">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="6" spans="1:36" x14ac:dyDescent="0.25">
       <c r="A6" s="1" t="s">
-        <v>63</v>
+        <v>46</v>
       </c>
       <c r="B6" s="1" t="s">
-        <v>18</v>
+        <v>9</v>
       </c>
       <c r="C6" s="1" t="s">
         <v>16</v>
@@ -1124,11 +3032,13 @@
         <v>17</v>
       </c>
       <c r="E6" s="1" t="s">
-        <v>70</v>
-      </c>
-      <c r="F6" s="1"/>
+        <v>68</v>
+      </c>
+      <c r="F6" s="1" t="s">
+        <v>69</v>
+      </c>
       <c r="G6" s="1" t="s">
-        <v>42</v>
+        <v>10</v>
       </c>
       <c r="H6" s="1" t="s">
         <v>11</v>
@@ -1136,42 +3046,13 @@
       <c r="I6" s="1" t="s">
         <v>12</v>
       </c>
-      <c r="J6" s="1"/>
-      <c r="K6" s="1"/>
-      <c r="L6" s="1" t="s">
-        <v>62</v>
-      </c>
-      <c r="O6" s="1" t="s">
-        <v>40</v>
-      </c>
-      <c r="P6" s="1" t="s">
-        <v>64</v>
-      </c>
-      <c r="Q6" s="1" t="s">
-        <v>52</v>
-      </c>
-      <c r="R6" s="1" t="s">
-        <v>53</v>
-      </c>
-      <c r="S6" s="1" t="s">
-        <v>23</v>
-      </c>
-      <c r="T6" s="1" t="s">
-        <v>69</v>
-      </c>
-      <c r="U6" s="1" t="s">
-        <v>26</v>
-      </c>
-      <c r="V6" s="1" t="s">
-        <v>27</v>
-      </c>
-    </row>
-    <row r="7" spans="1:30" x14ac:dyDescent="0.25">
+    </row>
+    <row r="7" spans="1:36" x14ac:dyDescent="0.25">
       <c r="A7" s="1" t="s">
-        <v>65</v>
+        <v>48</v>
       </c>
       <c r="B7" s="1" t="s">
-        <v>9</v>
+        <v>18</v>
       </c>
       <c r="C7" s="1" t="s">
         <v>16</v>
@@ -1180,13 +3061,11 @@
         <v>17</v>
       </c>
       <c r="E7" s="1" t="s">
-        <v>72</v>
-      </c>
-      <c r="F7" s="1" t="s">
-        <v>73</v>
-      </c>
+        <v>70</v>
+      </c>
+      <c r="F7" s="1"/>
       <c r="G7" s="1" t="s">
-        <v>19</v>
+        <v>10</v>
       </c>
       <c r="H7" s="1" t="s">
         <v>11</v>
@@ -1196,32 +3075,1483 @@
       </c>
       <c r="J7" s="1"/>
       <c r="K7" s="1"/>
-      <c r="L7" s="1" t="s">
+    </row>
+    <row r="8" spans="1:36" x14ac:dyDescent="0.25">
+      <c r="A8" s="1" t="s">
+        <v>75</v>
+      </c>
+      <c r="B8" s="1" t="s">
+        <v>47</v>
+      </c>
+      <c r="C8" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="D8" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="E8" s="1" t="s">
+        <v>71</v>
+      </c>
+      <c r="F8" s="1"/>
+      <c r="G8" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="H8" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="I8" s="1" t="s">
+        <v>12</v>
+      </c>
+      <c r="J8" s="1" t="s">
+        <v>45</v>
+      </c>
+      <c r="K8" s="1" t="s">
+        <v>72</v>
+      </c>
+    </row>
+    <row r="9" spans="1:36" x14ac:dyDescent="0.25">
+      <c r="A9" s="1" t="s">
+        <v>60</v>
+      </c>
+      <c r="B9" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="C9" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="D9" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="E9" s="1" t="s">
+        <v>72</v>
+      </c>
+      <c r="F9" s="1"/>
+      <c r="G9" s="1" t="s">
+        <v>42</v>
+      </c>
+      <c r="H9" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="I9" s="1" t="s">
+        <v>12</v>
+      </c>
+      <c r="J9" s="1"/>
+      <c r="K9" s="1"/>
+      <c r="L9" s="1" t="s">
+        <v>58</v>
+      </c>
+      <c r="O9" s="1" t="s">
+        <v>40</v>
+      </c>
+      <c r="P9" s="1" t="s">
+        <v>59</v>
+      </c>
+      <c r="Q9" s="1" t="s">
+        <v>49</v>
+      </c>
+      <c r="R9" s="1" t="s">
+        <v>50</v>
+      </c>
+      <c r="S9" s="1" t="s">
+        <v>23</v>
+      </c>
+      <c r="T9" s="1" t="s">
+        <v>64</v>
+      </c>
+      <c r="U9" s="1" t="s">
+        <v>26</v>
+      </c>
+      <c r="V9" s="1" t="s">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="10" spans="1:36" x14ac:dyDescent="0.25">
+      <c r="A10" s="1" t="s">
+        <v>76</v>
+      </c>
+      <c r="B10" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="C10" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="D10" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="E10" s="1" t="s">
+        <v>73</v>
+      </c>
+      <c r="F10" s="1" t="s">
+        <v>72</v>
+      </c>
+      <c r="G10" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="H10" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="I10" s="1" t="s">
+        <v>12</v>
+      </c>
+      <c r="J10" s="1"/>
+      <c r="K10" s="1"/>
+      <c r="L10" s="1" t="s">
+        <v>58</v>
+      </c>
+      <c r="O10" s="1" t="s">
+        <v>40</v>
+      </c>
+      <c r="P10" s="1" t="s">
+        <v>61</v>
+      </c>
+      <c r="Q10" s="1" t="s">
+        <v>49</v>
+      </c>
+      <c r="R10" s="1" t="s">
         <v>62</v>
       </c>
-      <c r="O7" s="1" t="s">
-        <v>40</v>
-      </c>
-      <c r="P7" s="1" t="s">
-        <v>66</v>
-      </c>
-      <c r="Q7" s="1" t="s">
+      <c r="S10" s="1" t="s">
+        <v>23</v>
+      </c>
+      <c r="T10" s="1" t="s">
+        <v>63</v>
+      </c>
+      <c r="U10" s="1" t="s">
+        <v>26</v>
+      </c>
+      <c r="V10" s="1" t="s">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="11" spans="1:36" x14ac:dyDescent="0.25">
+      <c r="A11" s="1" t="s">
+        <v>48</v>
+      </c>
+      <c r="B11" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="C11" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="D11" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="E11" s="1" t="s">
+        <v>70</v>
+      </c>
+      <c r="F11" s="1"/>
+      <c r="G11" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="H11" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="I11" s="1" t="s">
+        <v>12</v>
+      </c>
+      <c r="J11" s="1"/>
+      <c r="K11" s="1"/>
+      <c r="AE11" s="1" t="s">
+        <v>82</v>
+      </c>
+      <c r="AF11" s="1"/>
+      <c r="AG11" s="1"/>
+      <c r="AH11" s="1"/>
+      <c r="AI11" s="1"/>
+      <c r="AJ11" s="1"/>
+    </row>
+    <row r="12" spans="1:36" x14ac:dyDescent="0.25">
+      <c r="A12" s="1" t="s">
+        <v>48</v>
+      </c>
+      <c r="B12" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="C12" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="D12" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="E12" s="1" t="s">
+        <v>70</v>
+      </c>
+      <c r="F12" s="1"/>
+      <c r="G12" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="H12" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="I12" s="1" t="s">
+        <v>12</v>
+      </c>
+      <c r="J12" s="1"/>
+      <c r="K12" s="1"/>
+      <c r="AE12" s="1" t="s">
+        <v>90</v>
+      </c>
+      <c r="AF12" s="1" t="s">
+        <v>83</v>
+      </c>
+      <c r="AG12" s="1" t="s">
+        <v>84</v>
+      </c>
+      <c r="AH12" s="1" t="s">
+        <v>89</v>
+      </c>
+      <c r="AI12" s="1" t="s">
+        <v>87</v>
+      </c>
+      <c r="AJ12" s="1" t="s">
+        <v>88</v>
+      </c>
+    </row>
+    <row r="15" spans="1:36" x14ac:dyDescent="0.25">
+      <c r="A15" s="1" t="s">
+        <v>60</v>
+      </c>
+      <c r="B15" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="C15" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="D15" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="E15" s="1" t="s">
+        <v>73</v>
+      </c>
+      <c r="F15" s="1" t="s">
+        <v>72</v>
+      </c>
+      <c r="G15" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="H15" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="I15" s="1" t="s">
+        <v>12</v>
+      </c>
+      <c r="J15" s="1"/>
+      <c r="K15" s="1"/>
+      <c r="L15" s="1" t="s">
+        <v>58</v>
+      </c>
+      <c r="O15" s="1" t="s">
+        <v>40</v>
+      </c>
+      <c r="P15" s="1" t="s">
+        <v>61</v>
+      </c>
+      <c r="Q15" s="1" t="s">
+        <v>49</v>
+      </c>
+      <c r="R15" s="1" t="s">
+        <v>62</v>
+      </c>
+      <c r="S15" s="1" t="s">
+        <v>23</v>
+      </c>
+      <c r="T15" s="1" t="s">
+        <v>63</v>
+      </c>
+      <c r="U15" s="1" t="s">
+        <v>26</v>
+      </c>
+      <c r="V15" s="1" t="s">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="17" spans="1:36" x14ac:dyDescent="0.25">
+      <c r="A17" s="1" t="s">
+        <v>48</v>
+      </c>
+      <c r="B17" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="C17" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="D17" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="E17" s="1" t="s">
+        <v>70</v>
+      </c>
+      <c r="F17" s="1"/>
+      <c r="G17" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="H17" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="I17" s="1" t="s">
+        <v>12</v>
+      </c>
+      <c r="J17" s="1"/>
+      <c r="K17" s="1"/>
+    </row>
+    <row r="18" spans="1:36" x14ac:dyDescent="0.25">
+      <c r="A18" s="1" t="s">
+        <v>75</v>
+      </c>
+      <c r="B18" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="C18" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="D18" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="E18" s="1" t="s">
+        <v>68</v>
+      </c>
+      <c r="F18" s="1" t="s">
+        <v>69</v>
+      </c>
+      <c r="G18" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="H18" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="I18" s="1" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="19" spans="1:36" x14ac:dyDescent="0.25">
+      <c r="A19" s="1" t="s">
+        <v>96</v>
+      </c>
+      <c r="B19" s="1" t="s">
+        <v>47</v>
+      </c>
+      <c r="C19" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="D19" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="E19" s="1" t="s">
+        <v>71</v>
+      </c>
+      <c r="F19" s="1"/>
+      <c r="G19" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="H19" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="I19" s="1" t="s">
+        <v>12</v>
+      </c>
+      <c r="J19" s="1" t="s">
+        <v>45</v>
+      </c>
+      <c r="K19" s="1" t="s">
+        <v>72</v>
+      </c>
+    </row>
+    <row r="20" spans="1:36" x14ac:dyDescent="0.25">
+      <c r="A20" s="1" t="s">
+        <v>76</v>
+      </c>
+      <c r="B20" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="C20" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="D20" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="E20" s="1" t="s">
+        <v>67</v>
+      </c>
+      <c r="F20" s="1" t="s">
+        <v>68</v>
+      </c>
+      <c r="G20" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="H20" s="1" t="s">
+        <v>77</v>
+      </c>
+      <c r="I20" s="1" t="s">
+        <v>12</v>
+      </c>
+      <c r="J20" s="1"/>
+      <c r="K20" s="1"/>
+      <c r="L20" s="1" t="s">
+        <v>20</v>
+      </c>
+      <c r="O20" s="1" t="s">
+        <v>40</v>
+      </c>
+      <c r="P20" s="1" t="s">
+        <v>65</v>
+      </c>
+      <c r="Q20" s="1" t="s">
+        <v>49</v>
+      </c>
+      <c r="R20" s="1" t="s">
+        <v>50</v>
+      </c>
+      <c r="S20" s="1" t="s">
+        <v>23</v>
+      </c>
+      <c r="T20" s="1" t="s">
+        <v>51</v>
+      </c>
+      <c r="U20" s="1" t="s">
+        <v>26</v>
+      </c>
+      <c r="V20" s="1" t="s">
+        <v>27</v>
+      </c>
+      <c r="W20" s="1" t="s">
+        <v>40</v>
+      </c>
+      <c r="X20" s="1" t="s">
         <v>52</v>
       </c>
-      <c r="R7" s="1" t="s">
+      <c r="Y20" s="1" t="s">
+        <v>53</v>
+      </c>
+      <c r="Z20" s="2" t="s">
+        <v>54</v>
+      </c>
+      <c r="AA20" s="1" t="s">
+        <v>23</v>
+      </c>
+      <c r="AB20" s="1" t="s">
+        <v>55</v>
+      </c>
+      <c r="AC20" s="1" t="s">
+        <v>41</v>
+      </c>
+      <c r="AD20" s="1" t="s">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="21" spans="1:36" x14ac:dyDescent="0.25">
+      <c r="A21" s="1" t="s">
+        <v>97</v>
+      </c>
+      <c r="B21" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="C21" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="D21" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="E21" s="1" t="s">
         <v>67</v>
       </c>
-      <c r="S7" s="1" t="s">
-        <v>23</v>
-      </c>
-      <c r="T7" s="1" t="s">
+      <c r="F21" s="1" t="s">
         <v>68</v>
       </c>
-      <c r="U7" s="1" t="s">
+      <c r="G21" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="H21" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="I21" s="1" t="s">
+        <v>12</v>
+      </c>
+      <c r="J21" s="1"/>
+      <c r="K21" s="1"/>
+      <c r="L21" s="1" t="s">
+        <v>20</v>
+      </c>
+      <c r="O21" s="1" t="s">
+        <v>40</v>
+      </c>
+      <c r="P21" s="1" t="s">
+        <v>65</v>
+      </c>
+      <c r="Q21" s="1" t="s">
+        <v>49</v>
+      </c>
+      <c r="R21" s="1" t="s">
+        <v>50</v>
+      </c>
+      <c r="S21" s="1" t="s">
+        <v>23</v>
+      </c>
+      <c r="T21" s="1" t="s">
+        <v>51</v>
+      </c>
+      <c r="U21" s="1" t="s">
         <v>26</v>
       </c>
-      <c r="V7" s="1" t="s">
-        <v>27</v>
+      <c r="V21" s="1" t="s">
+        <v>27</v>
+      </c>
+      <c r="W21" s="1" t="s">
+        <v>40</v>
+      </c>
+      <c r="X21" s="1" t="s">
+        <v>52</v>
+      </c>
+      <c r="Y21" s="1" t="s">
+        <v>53</v>
+      </c>
+      <c r="Z21" s="2" t="s">
+        <v>54</v>
+      </c>
+      <c r="AA21" s="1" t="s">
+        <v>23</v>
+      </c>
+      <c r="AB21" s="1" t="s">
+        <v>55</v>
+      </c>
+      <c r="AC21" s="1" t="s">
+        <v>41</v>
+      </c>
+      <c r="AD21" s="1" t="s">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="23" spans="1:36" x14ac:dyDescent="0.25">
+      <c r="A23" s="1" t="s">
+        <v>94</v>
+      </c>
+      <c r="B23" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="C23" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="D23" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="E23" s="1" t="s">
+        <v>67</v>
+      </c>
+      <c r="F23" s="1" t="s">
+        <v>68</v>
+      </c>
+      <c r="G23" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="H23" s="1" t="s">
+        <v>77</v>
+      </c>
+      <c r="I23" s="1" t="s">
+        <v>12</v>
+      </c>
+      <c r="J23" s="1"/>
+      <c r="K23" s="1"/>
+      <c r="L23" s="1" t="s">
+        <v>20</v>
+      </c>
+      <c r="O23" s="1" t="s">
+        <v>40</v>
+      </c>
+      <c r="P23" s="1" t="s">
+        <v>65</v>
+      </c>
+      <c r="Q23" s="1" t="s">
+        <v>49</v>
+      </c>
+      <c r="R23" s="1" t="s">
+        <v>50</v>
+      </c>
+      <c r="S23" s="1" t="s">
+        <v>23</v>
+      </c>
+      <c r="T23" s="1" t="s">
+        <v>51</v>
+      </c>
+      <c r="U23" s="1" t="s">
+        <v>26</v>
+      </c>
+      <c r="V23" s="1" t="s">
+        <v>27</v>
+      </c>
+      <c r="W23" s="1" t="s">
+        <v>40</v>
+      </c>
+      <c r="X23" s="1" t="s">
+        <v>52</v>
+      </c>
+      <c r="Y23" s="1" t="s">
+        <v>53</v>
+      </c>
+      <c r="Z23" s="2" t="s">
+        <v>54</v>
+      </c>
+      <c r="AA23" s="1" t="s">
+        <v>23</v>
+      </c>
+      <c r="AB23" s="1" t="s">
+        <v>55</v>
+      </c>
+      <c r="AC23" s="1" t="s">
+        <v>41</v>
+      </c>
+      <c r="AD23" s="1" t="s">
+        <v>27</v>
+      </c>
+      <c r="AE23" s="1" t="s">
+        <v>90</v>
+      </c>
+      <c r="AF23" s="1" t="s">
+        <v>83</v>
+      </c>
+      <c r="AG23" s="1" t="s">
+        <v>84</v>
+      </c>
+      <c r="AH23" s="1" t="s">
+        <v>89</v>
+      </c>
+      <c r="AI23" s="1" t="s">
+        <v>87</v>
+      </c>
+      <c r="AJ23" s="1" t="s">
+        <v>88</v>
+      </c>
+    </row>
+    <row r="24" spans="1:36" x14ac:dyDescent="0.25">
+      <c r="A24" s="1" t="s">
+        <v>95</v>
+      </c>
+      <c r="B24" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="C24" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="D24" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="E24" s="1" t="s">
+        <v>67</v>
+      </c>
+      <c r="F24" s="1" t="s">
+        <v>68</v>
+      </c>
+      <c r="G24" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="H24" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="I24" s="1" t="s">
+        <v>12</v>
+      </c>
+      <c r="J24" s="1"/>
+      <c r="K24" s="1"/>
+      <c r="L24" s="1" t="s">
+        <v>20</v>
+      </c>
+      <c r="O24" s="1" t="s">
+        <v>40</v>
+      </c>
+      <c r="P24" s="1" t="s">
+        <v>65</v>
+      </c>
+      <c r="Q24" s="1" t="s">
+        <v>49</v>
+      </c>
+      <c r="R24" s="1" t="s">
+        <v>50</v>
+      </c>
+      <c r="S24" s="1" t="s">
+        <v>23</v>
+      </c>
+      <c r="T24" s="1" t="s">
+        <v>51</v>
+      </c>
+      <c r="U24" s="1" t="s">
+        <v>26</v>
+      </c>
+      <c r="V24" s="1" t="s">
+        <v>27</v>
+      </c>
+      <c r="W24" s="1" t="s">
+        <v>40</v>
+      </c>
+      <c r="X24" s="1" t="s">
+        <v>52</v>
+      </c>
+      <c r="Y24" s="1" t="s">
+        <v>53</v>
+      </c>
+      <c r="Z24" s="2" t="s">
+        <v>54</v>
+      </c>
+      <c r="AA24" s="1" t="s">
+        <v>23</v>
+      </c>
+      <c r="AB24" s="1" t="s">
+        <v>55</v>
+      </c>
+      <c r="AC24" s="1" t="s">
+        <v>41</v>
+      </c>
+      <c r="AD24" s="1" t="s">
+        <v>27</v>
+      </c>
+      <c r="AE24" s="1" t="s">
+        <v>90</v>
+      </c>
+      <c r="AF24" s="1" t="s">
+        <v>83</v>
+      </c>
+      <c r="AG24" s="1" t="s">
+        <v>84</v>
+      </c>
+      <c r="AH24" s="1" t="s">
+        <v>89</v>
+      </c>
+      <c r="AI24" s="1" t="s">
+        <v>87</v>
+      </c>
+      <c r="AJ24" s="1" t="s">
+        <v>88</v>
+      </c>
+    </row>
+    <row r="25" spans="1:36" x14ac:dyDescent="0.25">
+      <c r="A25" s="1" t="s">
+        <v>92</v>
+      </c>
+      <c r="B25" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="C25" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="D25" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="E25" s="1" t="s">
+        <v>68</v>
+      </c>
+      <c r="F25" s="1" t="s">
+        <v>69</v>
+      </c>
+      <c r="G25" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="H25" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="I25" s="1" t="s">
+        <v>12</v>
+      </c>
+      <c r="AE25" s="1" t="s">
+        <v>90</v>
+      </c>
+      <c r="AF25" s="1" t="s">
+        <v>83</v>
+      </c>
+      <c r="AG25" s="1" t="s">
+        <v>84</v>
+      </c>
+      <c r="AH25" s="1" t="s">
+        <v>89</v>
+      </c>
+      <c r="AI25" s="1" t="s">
+        <v>87</v>
+      </c>
+      <c r="AJ25" s="1" t="s">
+        <v>88</v>
+      </c>
+    </row>
+    <row r="26" spans="1:36" x14ac:dyDescent="0.25">
+      <c r="A26" s="1" t="s">
+        <v>93</v>
+      </c>
+      <c r="B26" s="1" t="s">
+        <v>47</v>
+      </c>
+      <c r="C26" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="D26" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="E26" s="1" t="s">
+        <v>71</v>
+      </c>
+      <c r="F26" s="1"/>
+      <c r="G26" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="H26" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="I26" s="1" t="s">
+        <v>12</v>
+      </c>
+      <c r="J26" s="1" t="s">
+        <v>45</v>
+      </c>
+      <c r="K26" s="1" t="s">
+        <v>72</v>
+      </c>
+      <c r="AE26" s="1" t="s">
+        <v>90</v>
+      </c>
+      <c r="AF26" s="1" t="s">
+        <v>83</v>
+      </c>
+      <c r="AG26" s="1" t="s">
+        <v>84</v>
+      </c>
+      <c r="AH26" s="1" t="s">
+        <v>89</v>
+      </c>
+      <c r="AI26" s="1" t="s">
+        <v>87</v>
+      </c>
+      <c r="AJ26" s="1" t="s">
+        <v>88</v>
+      </c>
+    </row>
+    <row r="27" spans="1:36" x14ac:dyDescent="0.25">
+      <c r="A27" s="1" t="s">
+        <v>91</v>
+      </c>
+      <c r="B27" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="C27" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="D27" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="E27" s="1" t="s">
+        <v>70</v>
+      </c>
+      <c r="F27" s="1"/>
+      <c r="G27" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="H27" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="I27" s="1" t="s">
+        <v>12</v>
+      </c>
+      <c r="J27" s="1"/>
+      <c r="K27" s="1"/>
+      <c r="AE27" s="1" t="s">
+        <v>90</v>
+      </c>
+      <c r="AF27" s="1" t="s">
+        <v>83</v>
+      </c>
+      <c r="AG27" s="1" t="s">
+        <v>84</v>
+      </c>
+      <c r="AH27" s="1" t="s">
+        <v>89</v>
+      </c>
+      <c r="AI27" s="1" t="s">
+        <v>87</v>
+      </c>
+      <c r="AJ27" s="1" t="s">
+        <v>88</v>
+      </c>
+    </row>
+    <row r="28" spans="1:36" x14ac:dyDescent="0.25">
+      <c r="A28" s="1" t="s">
+        <v>92</v>
+      </c>
+      <c r="B28" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="C28" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="D28" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="E28" s="1" t="s">
+        <v>70</v>
+      </c>
+      <c r="F28" s="1"/>
+      <c r="G28" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="H28" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="I28" s="1" t="s">
+        <v>12</v>
+      </c>
+      <c r="AE28" s="1" t="s">
+        <v>90</v>
+      </c>
+      <c r="AF28" s="1" t="s">
+        <v>83</v>
+      </c>
+      <c r="AG28" s="1" t="s">
+        <v>84</v>
+      </c>
+      <c r="AH28" s="1" t="s">
+        <v>89</v>
+      </c>
+      <c r="AI28" s="1" t="s">
+        <v>87</v>
+      </c>
+      <c r="AJ28" s="1" t="s">
+        <v>88</v>
+      </c>
+    </row>
+    <row r="29" spans="1:36" x14ac:dyDescent="0.25">
+      <c r="A29" s="1" t="s">
+        <v>93</v>
+      </c>
+      <c r="B29" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="C29" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="D29" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="E29" s="1" t="s">
+        <v>70</v>
+      </c>
+      <c r="F29" s="1"/>
+      <c r="G29" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="H29" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="I29" s="1" t="s">
+        <v>12</v>
+      </c>
+      <c r="AE29" s="1" t="s">
+        <v>98</v>
+      </c>
+    </row>
+    <row r="31" spans="1:36" x14ac:dyDescent="0.25">
+      <c r="A31" s="1" t="s">
+        <v>94</v>
+      </c>
+      <c r="B31" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="C31" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="D31" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="E31" s="1" t="s">
+        <v>72</v>
+      </c>
+      <c r="F31" s="1"/>
+      <c r="G31" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="H31" s="1" t="s">
+        <v>77</v>
+      </c>
+      <c r="I31" s="1" t="s">
+        <v>12</v>
+      </c>
+      <c r="J31" s="1"/>
+      <c r="K31" s="1"/>
+      <c r="L31" s="1" t="s">
+        <v>20</v>
+      </c>
+      <c r="O31" s="1" t="s">
+        <v>40</v>
+      </c>
+      <c r="P31" s="1" t="s">
+        <v>65</v>
+      </c>
+      <c r="Q31" s="1" t="s">
+        <v>49</v>
+      </c>
+      <c r="R31" s="1" t="s">
+        <v>50</v>
+      </c>
+      <c r="S31" s="1" t="s">
+        <v>23</v>
+      </c>
+      <c r="T31" s="1" t="s">
+        <v>51</v>
+      </c>
+      <c r="U31" s="1" t="s">
+        <v>26</v>
+      </c>
+      <c r="V31" s="1" t="s">
+        <v>27</v>
+      </c>
+      <c r="W31" s="1" t="s">
+        <v>40</v>
+      </c>
+      <c r="X31" s="1" t="s">
+        <v>52</v>
+      </c>
+      <c r="Y31" s="1" t="s">
+        <v>53</v>
+      </c>
+      <c r="Z31" s="2" t="s">
+        <v>54</v>
+      </c>
+      <c r="AA31" s="1" t="s">
+        <v>23</v>
+      </c>
+      <c r="AB31" s="1" t="s">
+        <v>55</v>
+      </c>
+      <c r="AC31" s="1" t="s">
+        <v>41</v>
+      </c>
+      <c r="AD31" s="1" t="s">
+        <v>27</v>
+      </c>
+      <c r="AE31" s="1" t="s">
+        <v>90</v>
+      </c>
+      <c r="AF31" s="1" t="s">
+        <v>83</v>
+      </c>
+      <c r="AG31" s="1" t="s">
+        <v>84</v>
+      </c>
+      <c r="AH31" s="1" t="s">
+        <v>89</v>
+      </c>
+    </row>
+    <row r="32" spans="1:36" x14ac:dyDescent="0.25">
+      <c r="A32" s="1" t="s">
+        <v>95</v>
+      </c>
+      <c r="B32" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="C32" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="D32" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="E32" s="1" t="s">
+        <v>72</v>
+      </c>
+      <c r="F32" s="1"/>
+      <c r="G32" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="H32" s="1" t="s">
+        <v>77</v>
+      </c>
+      <c r="I32" s="1" t="s">
+        <v>12</v>
+      </c>
+      <c r="J32" s="1"/>
+      <c r="K32" s="1"/>
+      <c r="L32" s="1" t="s">
+        <v>20</v>
+      </c>
+      <c r="O32" s="1" t="s">
+        <v>40</v>
+      </c>
+      <c r="P32" s="1" t="s">
+        <v>65</v>
+      </c>
+      <c r="Q32" s="1" t="s">
+        <v>49</v>
+      </c>
+      <c r="R32" s="1" t="s">
+        <v>50</v>
+      </c>
+      <c r="S32" s="1" t="s">
+        <v>23</v>
+      </c>
+      <c r="T32" s="1" t="s">
+        <v>51</v>
+      </c>
+      <c r="U32" s="1" t="s">
+        <v>26</v>
+      </c>
+      <c r="V32" s="1" t="s">
+        <v>27</v>
+      </c>
+      <c r="W32" s="1" t="s">
+        <v>40</v>
+      </c>
+      <c r="X32" s="1" t="s">
+        <v>52</v>
+      </c>
+      <c r="Y32" s="1" t="s">
+        <v>53</v>
+      </c>
+      <c r="Z32" s="2" t="s">
+        <v>54</v>
+      </c>
+      <c r="AA32" s="1" t="s">
+        <v>23</v>
+      </c>
+      <c r="AB32" s="1" t="s">
+        <v>55</v>
+      </c>
+      <c r="AC32" s="1" t="s">
+        <v>41</v>
+      </c>
+      <c r="AD32" s="1" t="s">
+        <v>27</v>
+      </c>
+      <c r="AE32" s="1" t="s">
+        <v>82</v>
+      </c>
+    </row>
+    <row r="33" spans="1:37" x14ac:dyDescent="0.25">
+      <c r="A33" s="1" t="s">
+        <v>101</v>
+      </c>
+      <c r="B33" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="C33" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="D33" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="E33" s="1" t="s">
+        <v>102</v>
+      </c>
+      <c r="F33" s="1"/>
+      <c r="G33" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="H33" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="I33" s="1" t="s">
+        <v>12</v>
+      </c>
+      <c r="J33" s="1"/>
+      <c r="K33" s="1"/>
+      <c r="L33" s="1" t="s">
+        <v>20</v>
+      </c>
+      <c r="O33" s="1" t="s">
+        <v>40</v>
+      </c>
+      <c r="P33" s="1" t="s">
+        <v>65</v>
+      </c>
+      <c r="Q33" s="1" t="s">
+        <v>49</v>
+      </c>
+      <c r="R33" s="1" t="s">
+        <v>50</v>
+      </c>
+      <c r="S33" s="1" t="s">
+        <v>23</v>
+      </c>
+      <c r="T33" s="1" t="s">
+        <v>51</v>
+      </c>
+      <c r="U33" s="1" t="s">
+        <v>26</v>
+      </c>
+      <c r="V33" s="1" t="s">
+        <v>27</v>
+      </c>
+      <c r="W33" s="1" t="s">
+        <v>40</v>
+      </c>
+      <c r="X33" s="1" t="s">
+        <v>52</v>
+      </c>
+      <c r="Y33" s="1" t="s">
+        <v>53</v>
+      </c>
+      <c r="Z33" s="2" t="s">
+        <v>54</v>
+      </c>
+      <c r="AA33" s="1" t="s">
+        <v>23</v>
+      </c>
+      <c r="AB33" s="1" t="s">
+        <v>55</v>
+      </c>
+      <c r="AC33" s="1" t="s">
+        <v>41</v>
+      </c>
+      <c r="AD33" s="1" t="s">
+        <v>27</v>
+      </c>
+      <c r="AE33" s="1" t="s">
+        <v>90</v>
+      </c>
+      <c r="AF33" s="1" t="s">
+        <v>83</v>
+      </c>
+      <c r="AG33" s="1" t="s">
+        <v>84</v>
+      </c>
+      <c r="AH33" s="1" t="s">
+        <v>89</v>
+      </c>
+    </row>
+    <row r="34" spans="1:37" x14ac:dyDescent="0.25">
+      <c r="A34" s="1" t="s">
+        <v>103</v>
+      </c>
+      <c r="B34" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="C34" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="D34" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="E34" s="1" t="s">
+        <v>102</v>
+      </c>
+      <c r="F34" s="1"/>
+      <c r="G34" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="H34" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="I34" s="1" t="s">
+        <v>12</v>
+      </c>
+      <c r="J34" s="1"/>
+      <c r="K34" s="1"/>
+      <c r="L34" s="1" t="s">
+        <v>20</v>
+      </c>
+      <c r="O34" s="1" t="s">
+        <v>40</v>
+      </c>
+      <c r="P34" s="1" t="s">
+        <v>65</v>
+      </c>
+      <c r="Q34" s="1" t="s">
+        <v>49</v>
+      </c>
+      <c r="R34" s="1" t="s">
+        <v>50</v>
+      </c>
+      <c r="S34" s="1" t="s">
+        <v>23</v>
+      </c>
+      <c r="T34" s="1" t="s">
+        <v>51</v>
+      </c>
+      <c r="U34" s="1" t="s">
+        <v>26</v>
+      </c>
+      <c r="V34" s="1" t="s">
+        <v>27</v>
+      </c>
+      <c r="W34" s="1" t="s">
+        <v>40</v>
+      </c>
+      <c r="X34" s="1" t="s">
+        <v>52</v>
+      </c>
+      <c r="Y34" s="1" t="s">
+        <v>53</v>
+      </c>
+      <c r="Z34" s="2" t="s">
+        <v>54</v>
+      </c>
+      <c r="AA34" s="1" t="s">
+        <v>23</v>
+      </c>
+      <c r="AB34" s="1" t="s">
+        <v>55</v>
+      </c>
+      <c r="AC34" s="1" t="s">
+        <v>41</v>
+      </c>
+      <c r="AD34" s="1" t="s">
+        <v>27</v>
+      </c>
+      <c r="AE34" s="1" t="s">
+        <v>82</v>
+      </c>
+    </row>
+    <row r="35" spans="1:37" x14ac:dyDescent="0.25">
+      <c r="A35" s="1" t="s">
+        <v>91</v>
+      </c>
+      <c r="B35" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="C35" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="D35" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="E35" s="1" t="s">
+        <v>70</v>
+      </c>
+      <c r="F35" s="1"/>
+      <c r="G35" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="H35" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="I35" s="1" t="s">
+        <v>12</v>
+      </c>
+      <c r="AE35" s="1" t="s">
+        <v>82</v>
+      </c>
+      <c r="AK35" s="1" t="s">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="36" spans="1:37" x14ac:dyDescent="0.25">
+      <c r="A36" s="1" t="s">
+        <v>92</v>
+      </c>
+      <c r="B36" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="C36" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="D36" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="E36" s="1" t="s">
+        <v>70</v>
+      </c>
+      <c r="F36" s="1"/>
+      <c r="G36" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="H36" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="I36" s="1" t="s">
+        <v>12</v>
+      </c>
+      <c r="AE36" s="1" t="s">
+        <v>90</v>
+      </c>
+      <c r="AF36" s="1" t="s">
+        <v>83</v>
+      </c>
+      <c r="AG36" s="1" t="s">
+        <v>84</v>
+      </c>
+      <c r="AH36" s="1" t="s">
+        <v>89</v>
+      </c>
+      <c r="AI36" s="1" t="s">
+        <v>87</v>
+      </c>
+      <c r="AJ36" s="1" t="s">
+        <v>88</v>
+      </c>
+    </row>
+    <row r="37" spans="1:37" x14ac:dyDescent="0.25">
+      <c r="A37" s="1" t="s">
+        <v>103</v>
+      </c>
+      <c r="B37" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="C37" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="D37" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="E37" s="1" t="s">
+        <v>102</v>
+      </c>
+      <c r="F37" s="1"/>
+      <c r="G37" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="H37" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="I37" s="1" t="s">
+        <v>12</v>
+      </c>
+      <c r="J37" s="1"/>
+      <c r="K37" s="1"/>
+      <c r="L37" s="1" t="s">
+        <v>20</v>
+      </c>
+      <c r="O37" s="1" t="s">
+        <v>40</v>
+      </c>
+      <c r="P37" s="1" t="s">
+        <v>65</v>
+      </c>
+      <c r="Q37" s="1" t="s">
+        <v>49</v>
+      </c>
+      <c r="R37" s="1" t="s">
+        <v>50</v>
+      </c>
+      <c r="S37" s="1" t="s">
+        <v>23</v>
+      </c>
+      <c r="T37" s="1" t="s">
+        <v>51</v>
+      </c>
+      <c r="U37" s="1" t="s">
+        <v>26</v>
+      </c>
+      <c r="V37" s="1" t="s">
+        <v>27</v>
+      </c>
+      <c r="W37" s="1" t="s">
+        <v>40</v>
+      </c>
+      <c r="X37" s="1" t="s">
+        <v>52</v>
+      </c>
+      <c r="Y37" s="1" t="s">
+        <v>53</v>
+      </c>
+      <c r="Z37" s="2" t="s">
+        <v>54</v>
+      </c>
+      <c r="AA37" s="1" t="s">
+        <v>23</v>
+      </c>
+      <c r="AB37" s="1" t="s">
+        <v>55</v>
+      </c>
+      <c r="AC37" s="1" t="s">
+        <v>41</v>
+      </c>
+      <c r="AD37" s="1" t="s">
+        <v>27</v>
+      </c>
+      <c r="AE37" s="1" t="s">
+        <v>82</v>
+      </c>
+      <c r="AJ37" s="1" t="s">
+        <v>100</v>
       </c>
     </row>
   </sheetData>
